--- a/StructureDefinition-DDCCCoreDataSet.TR.xlsx
+++ b/StructureDefinition-DDCCCoreDataSet.TR.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T06:07:49+00:00</t>
+    <t>2023-11-14T21:40:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-DDCCCoreDataSet.TR.xlsx
+++ b/StructureDefinition-DDCCCoreDataSet.TR.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T21:40:28+00:00</t>
+    <t>2023-12-14T13:07:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-DDCCCoreDataSet.TR.xlsx
+++ b/StructureDefinition-DDCCCoreDataSet.TR.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:07:01+00:00</t>
+    <t>2023-12-14T13:50:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-DDCCCoreDataSet.TR.xlsx
+++ b/StructureDefinition-DDCCCoreDataSet.TR.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:50:56+00:00</t>
+    <t>2023-12-15T03:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-DDCCCoreDataSet.TR.xlsx
+++ b/StructureDefinition-DDCCCoreDataSet.TR.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T03:05:37+00:00</t>
+    <t>2024-01-19T16:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-DDCCCoreDataSet.TR.xlsx
+++ b/StructureDefinition-DDCCCoreDataSet.TR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="174">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:18:21+00:00</t>
+    <t>2024-04-24T00:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -222,9 +222,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DDCCCoreDataSet.certificate.extension</t>
   </si>
   <si>
@@ -282,9 +279,6 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DDCCCoreDataSet.certificate.issuer</t>
   </si>
   <si>
@@ -380,9 +374,6 @@
 </t>
   </si>
   <si>
-    <t>./low</t>
-  </si>
-  <si>
     <t>DDCCCoreDataSet.certificate.period.end</t>
   </si>
   <si>
@@ -399,9 +390,6 @@
   </si>
   <si>
     <t>Period.end</t>
-  </si>
-  <si>
-    <t>./high</t>
   </si>
   <si>
     <t>DDCCCoreDataSet.test</t>
@@ -866,7 +854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR31"/>
+  <dimension ref="A1:AQ31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.1328125" customWidth="true" bestFit="true"/>
@@ -903,14 +891,13 @@
     <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" hidden="true" width="8.0" customWidth="false"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="6.2421875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="20.78515625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="28.34765625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="26.0703125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="25.46484375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="84.25" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="27.9296875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="17.52734375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="20.78515625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="28.34765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="26.0703125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="25.46484375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="84.25" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="27.9296875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="17.52734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1033,9 +1020,6 @@
       <c r="AQ1" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AR1" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
@@ -1155,9 +1139,6 @@
         <v>37</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR2" t="s" s="2">
         <v>47</v>
       </c>
     </row>
@@ -1279,9 +1260,6 @@
         <v>37</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR3" t="s" s="2">
         <v>52</v>
       </c>
     </row>
@@ -1403,9 +1381,6 @@
         <v>37</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR4" t="s" s="2">
         <v>57</v>
       </c>
     </row>
@@ -1529,9 +1504,6 @@
       <c r="AQ5" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AR5" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -1633,7 +1605,7 @@
         <v>37</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>37</v>
@@ -1651,22 +1623,19 @@
         <v>37</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR6" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1685,16 +1654,16 @@
         <v>37</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1732,19 +1701,19 @@
         <v>37</v>
       </c>
       <c r="AB7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC7" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AC7" t="s" s="2">
+      <c r="AD7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE7" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AD7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE7" t="s" s="2">
+      <c r="AF7" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>38</v>
@@ -1756,10 +1725,10 @@
         <v>37</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>37</v>
@@ -1777,22 +1746,19 @@
         <v>37</v>
       </c>
       <c r="AQ7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR7" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1811,19 +1777,19 @@
         <v>44</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="O8" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>37</v>
@@ -1872,7 +1838,7 @@
         <v>37</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>38</v>
@@ -1884,10 +1850,10 @@
         <v>37</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>37</v>
@@ -1905,18 +1871,15 @@
         <v>37</v>
       </c>
       <c r="AQ8" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR8" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1939,13 +1902,13 @@
         <v>44</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1996,7 +1959,7 @@
         <v>37</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>43</v>
@@ -2026,21 +1989,18 @@
         <v>37</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AR9" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2066,10 +2026,10 @@
         <v>45</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2120,7 +2080,7 @@
         <v>37</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>38</v>
@@ -2155,16 +2115,13 @@
       <c r="AQ10" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AR10" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2190,10 +2147,10 @@
         <v>54</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2244,7 +2201,7 @@
         <v>37</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>43</v>
@@ -2277,18 +2234,15 @@
         <v>37</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR11" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2314,10 +2268,10 @@
         <v>54</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2368,7 +2322,7 @@
         <v>37</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>38</v>
@@ -2403,16 +2357,13 @@
       <c r="AQ12" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AR12" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2438,10 +2389,10 @@
         <v>45</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2492,7 +2443,7 @@
         <v>37</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>43</v>
@@ -2525,18 +2476,15 @@
         <v>37</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR13" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2559,13 +2507,13 @@
         <v>37</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2616,7 +2564,7 @@
         <v>37</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>38</v>
@@ -2628,7 +2576,7 @@
         <v>37</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>37</v>
@@ -2646,21 +2594,18 @@
         <v>37</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AR14" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2755,7 +2700,7 @@
         <v>37</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>37</v>
@@ -2773,22 +2718,19 @@
         <v>37</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR15" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2807,16 +2749,16 @@
         <v>37</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2854,19 +2796,19 @@
         <v>37</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>38</v>
@@ -2878,10 +2820,10 @@
         <v>37</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>37</v>
@@ -2899,18 +2841,15 @@
         <v>37</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR16" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2933,16 +2872,16 @@
         <v>44</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2992,7 +2931,7 @@
         <v>37</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>38</v>
@@ -3001,13 +2940,13 @@
         <v>43</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>62</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>37</v>
@@ -3025,18 +2964,15 @@
         <v>37</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR17" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3059,23 +2995,23 @@
         <v>44</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q18" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="R18" t="s" s="2">
         <v>37</v>
@@ -3120,7 +3056,7 @@
         <v>37</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>38</v>
@@ -3129,13 +3065,13 @@
         <v>43</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>62</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>37</v>
@@ -3153,18 +3089,15 @@
         <v>37</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR18" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3190,10 +3123,10 @@
         <v>59</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3244,7 +3177,7 @@
         <v>37</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>43</v>
@@ -3279,16 +3212,13 @@
       <c r="AQ19" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AR19" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3383,7 +3313,7 @@
         <v>37</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>37</v>
@@ -3401,22 +3331,19 @@
         <v>37</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR20" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3435,16 +3362,16 @@
         <v>37</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3482,19 +3409,19 @@
         <v>37</v>
       </c>
       <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AC21" t="s" s="2">
+      <c r="AD21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE21" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AD21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE21" t="s" s="2">
+      <c r="AF21" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>38</v>
@@ -3506,10 +3433,10 @@
         <v>37</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>37</v>
@@ -3527,22 +3454,19 @@
         <v>37</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR21" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3561,19 +3485,19 @@
         <v>44</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>37</v>
@@ -3622,7 +3546,7 @@
         <v>37</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>38</v>
@@ -3634,10 +3558,10 @@
         <v>37</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>37</v>
@@ -3655,18 +3579,15 @@
         <v>37</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR22" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3689,13 +3610,13 @@
         <v>44</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3722,11 +3643,11 @@
         <v>37</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>37</v>
@@ -3744,7 +3665,7 @@
         <v>37</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>43</v>
@@ -3765,10 +3686,10 @@
         <v>37</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>37</v>
@@ -3777,18 +3698,15 @@
         <v>37</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR23" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3811,13 +3729,13 @@
         <v>44</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3844,11 +3762,11 @@
         <v>37</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>37</v>
@@ -3866,51 +3784,48 @@
         <v>37</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="AL24" t="s" s="2">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR24" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3933,13 +3848,13 @@
         <v>44</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3990,7 +3905,7 @@
         <v>37</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
@@ -4011,10 +3926,10 @@
         <v>37</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>37</v>
@@ -4023,18 +3938,15 @@
         <v>37</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR25" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4057,13 +3969,13 @@
         <v>44</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4114,7 +4026,7 @@
         <v>37</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
@@ -4135,10 +4047,10 @@
         <v>37</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>150</v>
+        <v>37</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>37</v>
@@ -4147,18 +4059,15 @@
         <v>37</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR26" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4181,13 +4090,13 @@
         <v>44</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4214,11 +4123,11 @@
         <v>37</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>37</v>
@@ -4236,7 +4145,7 @@
         <v>37</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
@@ -4251,13 +4160,13 @@
         <v>37</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>156</v>
+        <v>37</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>37</v>
@@ -4269,18 +4178,15 @@
         <v>37</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR27" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4303,13 +4209,13 @@
         <v>44</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4360,51 +4266,48 @@
         <v>37</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>160</v>
-      </c>
       <c r="AM28" t="s" s="2">
-        <v>161</v>
+        <v>37</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>163</v>
+        <v>37</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR28" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4427,13 +4330,13 @@
         <v>37</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4460,11 +4363,11 @@
         <v>37</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>37</v>
@@ -4482,7 +4385,7 @@
         <v>37</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -4497,10 +4400,10 @@
         <v>37</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>37</v>
+        <v>164</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>37</v>
@@ -4515,18 +4418,15 @@
         <v>37</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR29" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4549,13 +4449,13 @@
         <v>37</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4606,7 +4506,7 @@
         <v>37</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>38</v>
@@ -4633,24 +4533,21 @@
         <v>37</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>172</v>
+        <v>37</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR30" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4673,13 +4570,13 @@
         <v>44</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4706,11 +4603,11 @@
         <v>37</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>37</v>
@@ -4728,42 +4625,39 @@
         <v>37</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="AP31" t="s" s="2">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AR31" t="s" s="2">
         <v>37</v>
       </c>
     </row>
